--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5164,6 +5164,356 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120110497</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>339514</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6433090</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120110526</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>339514</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6433090</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120110576</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>339497</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6433101</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5166,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120110497</v>
+        <v>120110526</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>96175</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5178,35 +5178,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5254,7 +5258,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5263,6 +5267,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5281,10 +5286,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110526</v>
+        <v>120110497</v>
       </c>
       <c r="B41" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5293,39 +5298,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5373,7 +5374,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,7 +5383,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5286,10 +5286,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110497</v>
+        <v>120110576</v>
       </c>
       <c r="B41" t="n">
-        <v>57326</v>
+        <v>96175</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5298,35 +5298,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5334,10 +5338,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339514</v>
+        <v>339497</v>
       </c>
       <c r="R41" t="n">
-        <v>6433090</v>
+        <v>6433101</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5372,17 +5376,13 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120110576</v>
+        <v>120110497</v>
       </c>
       <c r="B42" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5413,39 +5413,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5453,10 +5449,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>339497</v>
+        <v>339514</v>
       </c>
       <c r="R42" t="n">
-        <v>6433101</v>
+        <v>6433090</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5491,13 +5487,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,10 +5038,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119802411</v>
+        <v>120110526</v>
       </c>
       <c r="B39" t="n">
-        <v>91842</v>
+        <v>96175</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5050,53 +5050,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>788</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söder om Mickelsdam, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>338931</v>
+        <v>339514</v>
       </c>
       <c r="R39" t="n">
-        <v>6433177</v>
+        <v>6433090</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5123,17 +5120,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Sammanväxta fruktkroppar växande invind/på roten av gran i mossig granskog</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5146,27 +5143,22 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Otto Nilsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Otto Nilsson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120110526</v>
+        <v>120110576</v>
       </c>
       <c r="B40" t="n">
         <v>96175</v>
@@ -5201,7 +5193,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5218,10 +5210,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>339514</v>
+        <v>339497</v>
       </c>
       <c r="R40" t="n">
-        <v>6433090</v>
+        <v>6433101</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5254,11 +5246,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5286,10 +5273,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110576</v>
+        <v>120110497</v>
       </c>
       <c r="B41" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5298,39 +5285,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5338,10 +5321,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339497</v>
+        <v>339514</v>
       </c>
       <c r="R41" t="n">
-        <v>6433101</v>
+        <v>6433090</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5376,13 +5359,17 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5401,14 +5388,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120110497</v>
+        <v>119802411</v>
       </c>
       <c r="B42" t="n">
-        <v>57326</v>
+        <v>91842</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5417,42 +5404,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>788</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Söder om Mickelsdam, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>339514</v>
+        <v>338931</v>
       </c>
       <c r="R42" t="n">
-        <v>6433090</v>
+        <v>6433177</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5479,17 +5473,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Sammanväxta fruktkroppar växande invind/på roten av gran i mossig granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5498,18 +5492,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,10 +5038,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110526</v>
+        <v>120110497</v>
       </c>
       <c r="B39" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5050,39 +5050,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5130,7 +5126,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5139,7 +5135,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5158,7 +5153,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120110576</v>
+        <v>120110526</v>
       </c>
       <c r="B40" t="n">
         <v>96175</v>
@@ -5193,7 +5188,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5210,10 +5205,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>339497</v>
+        <v>339514</v>
       </c>
       <c r="R40" t="n">
-        <v>6433101</v>
+        <v>6433090</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5246,6 +5241,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5273,10 +5273,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110497</v>
+        <v>120110576</v>
       </c>
       <c r="B41" t="n">
-        <v>57326</v>
+        <v>96175</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5285,35 +5285,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5321,10 +5325,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339514</v>
+        <v>339497</v>
       </c>
       <c r="R41" t="n">
-        <v>6433090</v>
+        <v>6433101</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5359,17 +5363,13 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5041,7 +5041,7 @@
         <v>120110497</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>120110526</v>
       </c>
       <c r="B40" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>120110576</v>
       </c>
       <c r="B41" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>119802411</v>
       </c>
       <c r="B42" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,10 +5038,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110497</v>
+        <v>120110526</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5050,35 +5050,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5126,7 +5130,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5135,6 +5139,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5153,10 +5158,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120110526</v>
+        <v>120110497</v>
       </c>
       <c r="B40" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5165,39 +5170,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5245,7 +5246,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5254,7 +5255,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,7 +5038,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110526</v>
+        <v>120110576</v>
       </c>
       <c r="B39" t="n">
         <v>96198</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>339514</v>
+        <v>339497</v>
       </c>
       <c r="R39" t="n">
-        <v>6433090</v>
+        <v>6433101</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5126,11 +5126,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5273,7 +5268,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110576</v>
+        <v>120110526</v>
       </c>
       <c r="B41" t="n">
         <v>96198</v>
@@ -5308,7 +5303,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339497</v>
+        <v>339514</v>
       </c>
       <c r="R41" t="n">
-        <v>6433101</v>
+        <v>6433090</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5361,6 +5356,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,7 +5038,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110576</v>
+        <v>120110526</v>
       </c>
       <c r="B39" t="n">
         <v>96198</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>339497</v>
+        <v>339514</v>
       </c>
       <c r="R39" t="n">
-        <v>6433101</v>
+        <v>6433090</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5126,6 +5126,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5268,7 +5273,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120110526</v>
+        <v>120110576</v>
       </c>
       <c r="B41" t="n">
         <v>96198</v>
@@ -5303,7 +5308,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339514</v>
+        <v>339497</v>
       </c>
       <c r="R41" t="n">
-        <v>6433090</v>
+        <v>6433101</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5356,11 +5361,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5038,10 +5038,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110526</v>
+        <v>120110497</v>
       </c>
       <c r="B39" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5050,39 +5050,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5130,7 +5126,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5139,7 +5135,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5158,10 +5153,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120110497</v>
+        <v>120110526</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5170,35 +5165,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5246,7 +5245,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5255,6 +5254,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121359908</v>
+        <v>121363305</v>
       </c>
       <c r="B43" t="n">
-        <v>91952</v>
+        <v>91975</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,37 +5528,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5567,10 +5559,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R43" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5607,7 +5599,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5635,10 +5627,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363305</v>
+        <v>121359908</v>
       </c>
       <c r="B44" t="n">
-        <v>91965</v>
+        <v>91962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5647,29 +5639,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R44" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5749,7 +5749,7 @@
         <v>121363230</v>
       </c>
       <c r="B45" t="n">
-        <v>91965</v>
+        <v>91975</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,7 +5516,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B43" t="n">
         <v>91975</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R43" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363230</v>
+        <v>121363305</v>
       </c>
       <c r="B45" t="n">
         <v>91975</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R45" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5519,7 +5519,7 @@
         <v>121363230</v>
       </c>
       <c r="B43" t="n">
-        <v>91975</v>
+        <v>91987</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121359908</v>
+        <v>121363305</v>
       </c>
       <c r="B44" t="n">
-        <v>91962</v>
+        <v>91987</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5639,37 +5639,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5670,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R44" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5710,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,10 +5738,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363305</v>
+        <v>121359908</v>
       </c>
       <c r="B45" t="n">
-        <v>91975</v>
+        <v>91974</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5758,29 +5750,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R45" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5519,7 +5519,7 @@
         <v>121363230</v>
       </c>
       <c r="B43" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363305</v>
+        <v>121359908</v>
       </c>
       <c r="B44" t="n">
-        <v>91987</v>
+        <v>91975</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5639,29 +5639,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5670,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R44" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5710,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5738,10 +5746,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121359908</v>
+        <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>91974</v>
+        <v>91988</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5750,37 +5758,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R45" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5519,7 +5519,7 @@
         <v>121363230</v>
       </c>
       <c r="B43" t="n">
-        <v>91988</v>
+        <v>91991</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>121359908</v>
       </c>
       <c r="B44" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>91988</v>
+        <v>91991</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121363230</v>
+        <v>121359908</v>
       </c>
       <c r="B43" t="n">
-        <v>91991</v>
+        <v>91984</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,29 +5528,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5599,7 +5607,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5627,10 +5635,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121359908</v>
+        <v>121363230</v>
       </c>
       <c r="B44" t="n">
-        <v>91978</v>
+        <v>91997</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5639,37 +5647,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>91991</v>
+        <v>91997</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121359908</v>
+        <v>121363230</v>
       </c>
       <c r="B43" t="n">
-        <v>91984</v>
+        <v>91998</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,37 +5528,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5607,7 +5599,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5635,10 +5627,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363230</v>
+        <v>121359908</v>
       </c>
       <c r="B44" t="n">
-        <v>91997</v>
+        <v>91985</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5647,29 +5639,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,7 +5516,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121363230</v>
+        <v>121363305</v>
       </c>
       <c r="B43" t="n">
         <v>91998</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R43" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B45" t="n">
         <v>91998</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R45" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121363305</v>
+        <v>121359908</v>
       </c>
       <c r="B43" t="n">
-        <v>91998</v>
+        <v>91985</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,29 +5528,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5559,10 +5567,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R43" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5599,7 +5607,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5627,10 +5635,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121359908</v>
+        <v>121363305</v>
       </c>
       <c r="B44" t="n">
-        <v>91985</v>
+        <v>91998</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5639,37 +5647,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R44" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5516,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121359908</v>
+        <v>121363305</v>
       </c>
       <c r="B43" t="n">
-        <v>91985</v>
+        <v>91998</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,37 +5528,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>788</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5567,10 +5559,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R43" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5607,7 +5599,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5635,7 +5627,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B44" t="n">
         <v>91998</v>
@@ -5678,10 +5670,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R44" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5710,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,10 +5738,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363230</v>
+        <v>121359908</v>
       </c>
       <c r="B45" t="n">
-        <v>91998</v>
+        <v>91985</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5758,29 +5750,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5635,7 +5635,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363230</v>
+        <v>121363305</v>
       </c>
       <c r="B44" t="n">
         <v>92006</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R44" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B45" t="n">
         <v>92006</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R45" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5635,7 +5635,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B44" t="n">
         <v>92006</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R44" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363230</v>
+        <v>121363305</v>
       </c>
       <c r="B45" t="n">
         <v>92006</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R45" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5635,10 +5635,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121363305</v>
+        <v>121363230</v>
       </c>
       <c r="B44" t="n">
-        <v>92006</v>
+        <v>92020</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338715</v>
+        <v>338746</v>
       </c>
       <c r="R44" t="n">
-        <v>6433097</v>
+        <v>6433099</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,10 +5746,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121363230</v>
+        <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>92006</v>
+        <v>92020</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338746</v>
+        <v>338715</v>
       </c>
       <c r="R45" t="n">
-        <v>6433099</v>
+        <v>6433097</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5638,7 +5638,7 @@
         <v>121363230</v>
       </c>
       <c r="B44" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5638,7 +5638,7 @@
         <v>121363230</v>
       </c>
       <c r="B44" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5638,7 +5638,7 @@
         <v>121363230</v>
       </c>
       <c r="B44" t="n">
-        <v>92023</v>
+        <v>92032</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>121363305</v>
       </c>
       <c r="B45" t="n">
-        <v>92023</v>
+        <v>92032</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,64 +812,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94983318</v>
+        <v>111964643</v>
       </c>
       <c r="B3" t="n">
-        <v>91623</v>
+        <v>95020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hydnellum, Vg</t>
+          <t>Gäddevadsbäcken, sydväst om Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339361</v>
+        <v>338568</v>
       </c>
       <c r="R3" t="n">
-        <v>6433082</v>
+        <v>6433172</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,12 +886,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växte alldeles intill en murken låga, ca 30 m SO om Gäddevadsbäcken.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,30 +909,35 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hedgranskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gles granskog</t>
+          <t>Äldre granskog med mycket lågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111964643</v>
+        <v>112010157</v>
       </c>
       <c r="B4" t="n">
-        <v>95020</v>
+        <v>90804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,42 +946,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, sydväst om Mickelsdamm, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338568</v>
+        <v>338723</v>
       </c>
       <c r="R4" t="n">
-        <v>6433172</v>
+        <v>6433094</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,17 +1015,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växte alldeles intill en murken låga, ca 30 m SO om Gäddevadsbäcken.</t>
+          <t>Växte i mossig blåbärsgranskog med inslag av tall. 2 m till en medelgrov gran, 10 m till en medelgrov tall. 25 m åt nordost växte en stor Ramaria.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,16 +1037,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Hedgranskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre granskog med mycket lågor</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112010157</v>
+        <v>112118170</v>
       </c>
       <c r="B5" t="n">
-        <v>90804</v>
+        <v>90874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,30 +1065,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,14 +1100,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338723</v>
+        <v>338724</v>
       </c>
       <c r="R5" t="n">
-        <v>6433094</v>
+        <v>6433096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växte i mossig blåbärsgranskog med inslag av tall. 2 m till en medelgrov gran, 10 m till en medelgrov tall. 25 m åt nordost växte en stor Ramaria.</t>
+          <t>Ett mycel. Även färsk f k.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,73 +1160,71 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112010327</v>
+        <v>112118159</v>
       </c>
       <c r="B6" t="n">
-        <v>91623</v>
+        <v>5123</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339353</v>
+        <v>338583</v>
       </c>
       <c r="R6" t="n">
-        <v>6433091</v>
+        <v>6433159</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1253,17 +1251,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte i medelgrov granskog. Var utspridda på 7 olika fläckar inom en cirkel på 15-20 m.</t>
+          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,22 +1277,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112118170</v>
+        <v>112118128</v>
       </c>
       <c r="B7" t="n">
-        <v>90874</v>
+        <v>95059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,34 +1305,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1342,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338724</v>
+        <v>338530</v>
       </c>
       <c r="R7" t="n">
-        <v>6433096</v>
+        <v>6433165</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1378,11 +1377,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett mycel. Även färsk f k.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112118159</v>
+        <v>112118167</v>
       </c>
       <c r="B8" t="n">
-        <v>5123</v>
+        <v>90874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,32 +1420,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1459,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338583</v>
+        <v>338714</v>
       </c>
       <c r="R8" t="n">
-        <v>6433159</v>
+        <v>6433095</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1499,7 +1495,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
+          <t>Vid basen av äldre gran. Gamla f k.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112118128</v>
+        <v>112118130</v>
       </c>
       <c r="B9" t="n">
-        <v>95059</v>
+        <v>93269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,33 +1539,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1617,6 +1605,11 @@
           <t>2023-09-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1642,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112118167</v>
+        <v>112118162</v>
       </c>
       <c r="B10" t="n">
-        <v>90874</v>
+        <v>5145</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,34 +1651,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338714</v>
+        <v>338583</v>
       </c>
       <c r="R10" t="n">
-        <v>6433095</v>
+        <v>6433159</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1733,7 +1724,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vid basen av äldre gran. Gamla f k.</t>
+          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112118130</v>
+        <v>112221530</v>
       </c>
       <c r="B11" t="n">
-        <v>93269</v>
+        <v>90842</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,42 +1764,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>150</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338530</v>
+        <v>338720</v>
       </c>
       <c r="R11" t="n">
-        <v>6433165</v>
+        <v>6433100</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,17 +1833,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ca antal. Även övermogna fruktkroppar. Sannolikt samma där arten obsats tidigare i september.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112118162</v>
+        <v>112221660</v>
       </c>
       <c r="B12" t="n">
-        <v>5145</v>
+        <v>90874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,43 +1887,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Gäddevadsbäcken, söder om. , Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338583</v>
+        <v>338727</v>
       </c>
       <c r="R12" t="n">
-        <v>6433159</v>
+        <v>6433110</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1952,17 +1952,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,10 +1985,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112221530</v>
+        <v>112234897</v>
       </c>
       <c r="B13" t="n">
-        <v>90842</v>
+        <v>99036</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,49 +1997,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338720</v>
+        <v>338737</v>
       </c>
       <c r="R13" t="n">
-        <v>6433100</v>
+        <v>6433098</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2071,17 +2063,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca antal. Även övermogna fruktkroppar. Sannolikt samma där arten obsats tidigare i september.</t>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,22 +2089,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112221660</v>
+        <v>112234040</v>
       </c>
       <c r="B14" t="n">
-        <v>90874</v>
+        <v>85238</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,30 +2113,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2156,14 +2148,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om. , Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338727</v>
+        <v>338742</v>
       </c>
       <c r="R14" t="n">
-        <v>6433110</v>
+        <v>6433095</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2190,12 +2182,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,22 +2208,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112234897</v>
+        <v>112283922</v>
       </c>
       <c r="B15" t="n">
-        <v>99036</v>
+        <v>89139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,35 +2232,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>256756</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338737</v>
+        <v>338719</v>
       </c>
       <c r="R15" t="n">
-        <v>6433098</v>
+        <v>6433105</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
+          <t>Samma fruktkropp som jag såg 2023-09-09. Denna gången var den äldre och jag mätte den till 21 cm hög och 29 cm bred. 1,5 m från gran och 6-7 m från tall. Det stod ny ytterligare en blek taggsvamp, en yngre fruktkropp ca 25 meter längre söderut denna gång.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,14 +2339,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112234040</v>
+        <v>112234006</v>
       </c>
       <c r="B16" t="n">
-        <v>85238</v>
+        <v>91607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2355,26 +2355,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>249278</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+          <t>En rejäl "tuva" med 75-100 fruktkroppar i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112283922</v>
+        <v>112233934</v>
       </c>
       <c r="B17" t="n">
-        <v>89139</v>
+        <v>90899</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,26 +2474,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256756</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338719</v>
+        <v>338742</v>
       </c>
       <c r="R17" t="n">
-        <v>6433105</v>
+        <v>6433095</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Samma fruktkropp som jag såg 2023-09-09. Denna gången var den äldre och jag mätte den till 21 cm hög och 29 cm bred. 1,5 m från gran och 6-7 m från tall. Det stod ny ytterligare en blek taggsvamp, en yngre fruktkropp ca 25 meter längre söderut denna gång.</t>
+          <t>Växte i en medelgrov granskog med inslag av framför allt tall. Växte 4 m från medelgrov tall, 2 m från klen gran och 4 m till medelgrov gran. Klart kalkpåverkad barrskog med flera andra kalkgynnade arter. Förekomst av blåsippa.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,10 +2577,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112234006</v>
+        <v>112234871</v>
       </c>
       <c r="B18" t="n">
-        <v>91607</v>
+        <v>91626</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,30 +2589,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338742</v>
+        <v>338747</v>
       </c>
       <c r="R18" t="n">
-        <v>6433095</v>
+        <v>6433099</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En rejäl "tuva" med 75-100 fruktkroppar i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte alldeles nära barrspindelskivling och blåsippa. Såg ut att vara den som bildar Mykorrhiza med gran, och gran stod närmast, men det stod även en medelgrov tall 8-10 m bort.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112233934</v>
+        <v>112319644</v>
       </c>
       <c r="B19" t="n">
-        <v>90899</v>
+        <v>95067</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,49 +2708,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338742</v>
+        <v>339683</v>
       </c>
       <c r="R19" t="n">
-        <v>6433095</v>
+        <v>6433113</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,17 +2778,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Växte i en medelgrov granskog med inslag av framför allt tall. Växte 4 m från medelgrov tall, 2 m från klen gran och 4 m till medelgrov gran. Klart kalkpåverkad barrskog med flera andra kalkgynnade arter. Förekomst av blåsippa.</t>
+          <t>Ca 0,5 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,26 +2804,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112234871</v>
+        <v>112319711</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>95067</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2831,45 +2832,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338747</v>
+        <v>339195</v>
       </c>
       <c r="R20" t="n">
-        <v>6433099</v>
+        <v>6433104</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2896,17 +2890,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte alldeles nära barrspindelskivling och blåsippa. Såg ut att vara den som bildar Mykorrhiza med gran, och gran stod närmast, men det stod även en medelgrov tall 8-10 m bort.</t>
+          <t>Några större tuvor.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2922,22 +2916,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112319644</v>
+        <v>112319668</v>
       </c>
       <c r="B21" t="n">
-        <v>95067</v>
+        <v>56477</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,39 +2940,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2986,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>339683</v>
+        <v>339565</v>
       </c>
       <c r="R21" t="n">
-        <v>6433113</v>
+        <v>6433114</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3026,7 +3016,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 0,5 kvm.</t>
+          <t>Vid basen av död gran mm</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3035,7 +3025,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3054,10 +3043,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112319711</v>
+        <v>112411671</v>
       </c>
       <c r="B22" t="n">
-        <v>95067</v>
+        <v>79356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3070,38 +3059,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>339195</v>
+        <v>339623</v>
       </c>
       <c r="R22" t="n">
-        <v>6433104</v>
+        <v>6433082</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3128,17 +3116,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Några större tuvor.</t>
+          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3154,22 +3142,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112319668</v>
+        <v>112411540</v>
       </c>
       <c r="B23" t="n">
-        <v>56477</v>
+        <v>83378</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3178,49 +3166,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3518</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>339565</v>
+        <v>339392</v>
       </c>
       <c r="R23" t="n">
-        <v>6433114</v>
+        <v>6433088</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3244,17 +3235,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vid basen av död gran mm</t>
+          <t>Växte i knappt medelgrov granskog med inslag av tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3263,28 +3254,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112411671</v>
+        <v>112411466</v>
       </c>
       <c r="B24" t="n">
-        <v>79356</v>
+        <v>95128</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3297,37 +3289,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>339623</v>
+        <v>339209</v>
       </c>
       <c r="R24" t="n">
-        <v>6433082</v>
+        <v>6433092</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3364,7 +3365,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
+          <t>Växte på marken intill en hassel med havstulpanlav. Här börjar det bli lite blockigt och tallen ingår här lite mer i trädbeståndet än lite längre ner i sluttningen, där medelgrov gran dominerar stort.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3392,47 +3393,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112411540</v>
+        <v>112411691</v>
       </c>
       <c r="B25" t="n">
-        <v>83378</v>
+        <v>91607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3518</v>
+        <v>788</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3443,13 +3444,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>339392</v>
+        <v>338738</v>
       </c>
       <c r="R25" t="n">
-        <v>6433088</v>
+        <v>6433093</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3483,7 +3484,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växte i knappt medelgrov granskog med inslag av tall.</t>
+          <t>Ett stort antal fruktkroppar satt gyttrat fördelade på några fläckar, ca 6 m väster om de djupa hjulspår som bäcken rinner i. 3 m till medelgrov tall och relativt grov gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3511,7 +3512,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112411499</v>
+        <v>112411553</v>
       </c>
       <c r="B26" t="n">
         <v>95128</v>
@@ -3546,7 +3547,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3559,14 +3560,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339346</v>
+        <v>339646</v>
       </c>
       <c r="R26" t="n">
-        <v>6433104</v>
+        <v>6433088</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3599,11 +3600,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växte på marken fördelat på några fläckar, i medelgrov granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,7 +3627,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112411466</v>
+        <v>112411563</v>
       </c>
       <c r="B27" t="n">
         <v>95128</v>
@@ -3666,12 +3662,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3679,14 +3675,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339209</v>
+        <v>339703</v>
       </c>
       <c r="R27" t="n">
-        <v>6433092</v>
+        <v>6433086</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3723,7 +3719,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växte på marken intill en hassel med havstulpanlav. Här börjar det bli lite blockigt och tallen ingår här lite mer i trädbeståndet än lite längre ner i sluttningen, där medelgrov gran dominerar stort.</t>
+          <t>Växte i flera fläckar inom en radie på 10 m. ganska mycket.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3751,61 +3747,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112411691</v>
+        <v>112411670</v>
       </c>
       <c r="B28" t="n">
-        <v>91607</v>
+        <v>95488</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>788</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>338738</v>
+        <v>339608</v>
       </c>
       <c r="R28" t="n">
-        <v>6433093</v>
+        <v>6433081</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3842,7 +3831,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett stort antal fruktkroppar satt gyttrat fördelade på några fläckar, ca 6 m väster om de djupa hjulspår som bäcken rinner i. 3 m till medelgrov tall och relativt grov gran.</t>
+          <t>Växte på en ek, strax ovanför den sydvända branten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,10 +3859,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112411553</v>
+        <v>112411635</v>
       </c>
       <c r="B29" t="n">
-        <v>95128</v>
+        <v>79356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3886,46 +3875,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339646</v>
+        <v>339209</v>
       </c>
       <c r="R29" t="n">
-        <v>6433088</v>
+        <v>6433092</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3958,6 +3938,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112411563</v>
+        <v>112431338</v>
       </c>
       <c r="B30" t="n">
-        <v>95128</v>
+        <v>5182</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4001,46 +3986,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339703</v>
+        <v>338710</v>
       </c>
       <c r="R30" t="n">
-        <v>6433086</v>
+        <v>6433103</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4067,17 +4049,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växte i flera fläckar inom en radie på 10 m. ganska mycket.</t>
+          <t>I senvuxen, klen gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,22 +4075,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112411670</v>
+        <v>112612655</v>
       </c>
       <c r="B31" t="n">
-        <v>95488</v>
+        <v>79468</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4121,27 +4103,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4149,10 +4130,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>339608</v>
+        <v>339754</v>
       </c>
       <c r="R31" t="n">
-        <v>6433081</v>
+        <v>6433067</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4179,17 +4160,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växte på en ek, strax ovanför den sydvända branten.</t>
+          <t>Växte på en av tre klena ekar som växte ihop.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,10 +4198,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112411635</v>
+        <v>112612271</v>
       </c>
       <c r="B32" t="n">
-        <v>79356</v>
+        <v>93798</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,37 +4214,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230185</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>339209</v>
+        <v>339627</v>
       </c>
       <c r="R32" t="n">
-        <v>6433092</v>
+        <v>6433093</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4290,17 +4280,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
+          <t>En lite större kudde som var 30 cm hög, 80 cm lång och 60 cm bred. Växte i skog med gran, tall och ek, lite norr om en sydvänd brant. Ganska lång trädkontinuitet med andra ord.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4328,10 +4318,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112431338</v>
+        <v>112613408</v>
       </c>
       <c r="B33" t="n">
-        <v>5182</v>
+        <v>91021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4340,47 +4330,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>150</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>338710</v>
+        <v>338726</v>
       </c>
       <c r="R33" t="n">
-        <v>6433103</v>
+        <v>6433094</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4407,17 +4399,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I senvuxen, klen gran.</t>
+          <t>Växte någon halvmeter från de grangråtickor som jag fann på platsen 2023-09-20. De gamla var det bara rester av, men dessa var lite yngre och kunde samlas in som kollekt.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4433,22 +4425,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112612655</v>
+        <v>120110526</v>
       </c>
       <c r="B34" t="n">
-        <v>79468</v>
+        <v>96198</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4461,37 +4453,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230185</v>
+        <v>2569</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>339754</v>
+        <v>339514</v>
       </c>
       <c r="R34" t="n">
-        <v>6433067</v>
+        <v>6433090</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4518,17 +4519,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växte på en av tre klena ekar som växte ihop.</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4556,10 +4557,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112613636</v>
+        <v>120110576</v>
       </c>
       <c r="B35" t="n">
-        <v>94594</v>
+        <v>96198</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4572,26 +4573,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4599,23 +4600,19 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>339233</v>
+        <v>339497</v>
       </c>
       <c r="R35" t="n">
-        <v>6433088</v>
+        <v>6433101</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4642,17 +4639,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Växte på en klen granlåga.</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4672,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112612271</v>
+        <v>120110497</v>
       </c>
       <c r="B36" t="n">
-        <v>93798</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,50 +4684,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>339627</v>
+        <v>339514</v>
       </c>
       <c r="R36" t="n">
-        <v>6433093</v>
+        <v>6433090</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4762,17 +4750,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>En lite större kudde som var 30 cm hög, 80 cm lång och 60 cm bred. Växte i skog med gran, tall och ek, lite norr om en sydvänd brant. Ganska lång trädkontinuitet med andra ord.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4781,7 +4769,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4800,10 +4787,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112613408</v>
+        <v>121359908</v>
       </c>
       <c r="B37" t="n">
-        <v>91021</v>
+        <v>91993</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4835,7 +4822,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4851,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>338726</v>
+        <v>338746</v>
       </c>
       <c r="R37" t="n">
-        <v>6433094</v>
+        <v>6433099</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4881,17 +4868,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växte någon halvmeter från de grangråtickor som jag fann på platsen 2023-09-20. De gamla var det bara rester av, men dessa var lite yngre och kunde samlas in som kollekt.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4912,58 +4899,49 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112612429</v>
+        <v>121363230</v>
       </c>
       <c r="B38" t="n">
-        <v>56478</v>
+        <v>92032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>788</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4971,13 +4949,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>339338</v>
+        <v>338746</v>
       </c>
       <c r="R38" t="n">
-        <v>6433073</v>
+        <v>6433099</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5001,17 +4979,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Skrämde upp den så att den bullrade iväg.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5020,6 +4998,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5031,69 +5010,60 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120110526</v>
+        <v>121363305</v>
       </c>
       <c r="B39" t="n">
-        <v>96198</v>
+        <v>92032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>788</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>339514</v>
+        <v>338715</v>
       </c>
       <c r="R39" t="n">
-        <v>6433090</v>
+        <v>6433097</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5120,17 +5090,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5151,709 +5121,10 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>120110576</v>
-      </c>
-      <c r="B40" t="n">
-        <v>96198</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Bazzania trilobata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>339497</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6433101</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>120110497</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>339514</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6433090</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>119802411</v>
-      </c>
-      <c r="B42" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>788</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hydnellum geogenium</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Söder om Mickelsdam, Vg</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>338931</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6433177</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Sammanväxta fruktkroppar växande invind/på roten av gran i mossig granskog</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Otto Nilsson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Otto Nilsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>121359908</v>
-      </c>
-      <c r="B43" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>150</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Mickelsdamm, söder om, Vg</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>338746</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6433099</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>121363230</v>
-      </c>
-      <c r="B44" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>788</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Hydnellum geogenium</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Mickelsdamm, söder om, Vg</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>338746</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6433099</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>121363305</v>
-      </c>
-      <c r="B45" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>788</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Hydnellum geogenium</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Mickelsdamm, söder om, Vg</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>338715</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6433097</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5126,6 +5126,339 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127816003</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92611</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>150</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>338721</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6433102</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127813879</v>
+      </c>
+      <c r="B41" t="n">
+        <v>95692</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>338706</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127820719</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>338683</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6433100</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>92611</v>
+        <v>92617</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>95692</v>
+        <v>95698</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>92617</v>
+        <v>92620</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>95698</v>
+        <v>95701</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>127820719</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>92620</v>
+        <v>92628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>95701</v>
+        <v>95709</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>127820719</v>
       </c>
       <c r="B42" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5128,52 +5128,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127816003</v>
+        <v>127813879</v>
       </c>
       <c r="B40" t="n">
-        <v>92628</v>
+        <v>95710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>2810</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>338721</v>
+        <v>338706</v>
       </c>
       <c r="R40" t="n">
-        <v>6433102</v>
+        <v>6433103</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5205,7 +5198,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5208,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,7 +5217,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5243,45 +5235,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127813879</v>
+        <v>127816003</v>
       </c>
       <c r="B41" t="n">
-        <v>95709</v>
+        <v>92629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2810</v>
+        <v>150</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>338706</v>
+        <v>338721</v>
       </c>
       <c r="R41" t="n">
-        <v>6433103</v>
+        <v>6433102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5313,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5323,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5332,6 +5331,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5128,45 +5128,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127813879</v>
+        <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>95710</v>
+        <v>92629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2810</v>
+        <v>150</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>338706</v>
+        <v>338721</v>
       </c>
       <c r="R40" t="n">
-        <v>6433103</v>
+        <v>6433102</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5198,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5208,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5217,6 +5224,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5235,52 +5243,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127816003</v>
+        <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>92629</v>
+        <v>95710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>150</v>
+        <v>2810</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>338721</v>
+        <v>338706</v>
       </c>
       <c r="R41" t="n">
-        <v>6433102</v>
+        <v>6433103</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5313,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5323,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,7 +5332,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>92629</v>
+        <v>92630</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>95710</v>
+        <v>95711</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127816003</v>
       </c>
       <c r="B40" t="n">
-        <v>92630</v>
+        <v>92631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127813879</v>
       </c>
       <c r="B41" t="n">
-        <v>95711</v>
+        <v>95712</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5128,52 +5128,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127816003</v>
+        <v>127813879</v>
       </c>
       <c r="B40" t="n">
-        <v>92631</v>
+        <v>95720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>2810</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>338721</v>
+        <v>338706</v>
       </c>
       <c r="R40" t="n">
-        <v>6433102</v>
+        <v>6433103</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5205,7 +5198,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5208,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,7 +5217,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5243,45 +5235,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127813879</v>
+        <v>127816003</v>
       </c>
       <c r="B41" t="n">
-        <v>95712</v>
+        <v>92639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2810</v>
+        <v>150</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>338706</v>
+        <v>338721</v>
       </c>
       <c r="R41" t="n">
-        <v>6433103</v>
+        <v>6433102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5313,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5323,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5332,6 +5331,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>127820719</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57667</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5131,7 +5131,7 @@
         <v>127813879</v>
       </c>
       <c r="B40" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>127816003</v>
       </c>
       <c r="B41" t="n">
-        <v>92639</v>
+        <v>92731</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>127820719</v>
       </c>
       <c r="B42" t="n">
-        <v>57667</v>
+        <v>57679</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5459,6 +5459,335 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128623143</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>338866</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6433122</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128623459</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>338878</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6433141</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128623098</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97198</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>338872</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6433142</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97198</v>
+        <v>97204</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97204</v>
+        <v>97210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97212</v>
+        <v>97213</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97213</v>
+        <v>97240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97240</v>
+        <v>97246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97246</v>
+        <v>97253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97253</v>
+        <v>97257</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97257</v>
+        <v>97264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,6 +5787,457 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129026915</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>338675</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129025873</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97514</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>338669</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6433141</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129025839</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97264</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>338674</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6433139</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129025860</v>
+      </c>
+      <c r="B49" t="n">
+        <v>95879</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>338675</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6433142</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97267</v>
+        <v>97272</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97272</v>
+        <v>97277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97272</v>
+        <v>97277</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5464,7 +5464,7 @@
         <v>128623143</v>
       </c>
       <c r="B43" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>128623459</v>
       </c>
       <c r="B44" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>128623098</v>
       </c>
       <c r="B45" t="n">
-        <v>97272</v>
+        <v>97280</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97277</v>
+        <v>97280</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97277</v>
+        <v>97280</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5793,7 +5793,7 @@
         <v>129026915</v>
       </c>
       <c r="B46" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97280</v>
+        <v>97290</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97280</v>
+        <v>97290</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97290</v>
+        <v>97297</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97290</v>
+        <v>97297</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5793,7 +5793,7 @@
         <v>129026915</v>
       </c>
       <c r="B46" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97297</v>
+        <v>97299</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97297</v>
+        <v>97299</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97299</v>
+        <v>97325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97299</v>
+        <v>97325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97333</v>
+        <v>97337</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97333</v>
+        <v>97337</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -5909,7 +5909,7 @@
         <v>129025873</v>
       </c>
       <c r="B47" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>129025839</v>
       </c>
       <c r="B48" t="n">
-        <v>97345</v>
+        <v>97348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>129025860</v>
       </c>
       <c r="B49" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129116850</v>
       </c>
       <c r="B50" t="n">
-        <v>97345</v>
+        <v>97348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1439777</v>
+        <v>111964643</v>
       </c>
       <c r="B2" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Risveden, Skår 1:39, Vg</t>
+          <t>Gäddevadsbäcken, sydväst om Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339396.7253430905</v>
+        <v>338568</v>
       </c>
       <c r="R2" t="n">
-        <v>6433141.280283828</v>
+        <v>6433172</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>fultig granskog</t>
+          <t>Växte alldeles intill en murken låga, ca 30 m SO om Gäddevadsbäcken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,44 +763,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hedgranskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Leif Danielson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>Äldre granskog med mycket lågor</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Leif Danielson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leif Danielson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111964643</v>
+        <v>112118128</v>
       </c>
       <c r="B3" t="n">
-        <v>95020</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,21 +820,29 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, sydväst om Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338568</v>
+        <v>338530</v>
       </c>
       <c r="R3" t="n">
-        <v>6433172</v>
+        <v>6433165</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,17 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växte alldeles intill en murken låga, ca 30 m SO om Gäddevadsbäcken.</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,75 +887,61 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Hedgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre granskog med mycket lågor</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112010157</v>
+        <v>112235807</v>
       </c>
       <c r="B4" t="n">
-        <v>90804</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338723</v>
+        <v>338607</v>
       </c>
       <c r="R4" t="n">
-        <v>6433094</v>
+        <v>6433097</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,17 +979,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växte i mossig blåbärsgranskog med inslag av tall. 2 m till en medelgrov gran, 10 m till en medelgrov tall. 25 m åt nordost växte en stor Ramaria.</t>
+          <t>Växte vid en äldre tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112118170</v>
+        <v>112118130</v>
       </c>
       <c r="B5" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,34 +1028,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338724</v>
+        <v>338530</v>
       </c>
       <c r="R5" t="n">
-        <v>6433096</v>
+        <v>6433165</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett mycel. Även färsk f k.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112118159</v>
+        <v>106197313</v>
       </c>
       <c r="B6" t="n">
-        <v>5123</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,46 +1135,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338583</v>
+        <v>338494</v>
       </c>
       <c r="R6" t="n">
-        <v>6433159</v>
+        <v>6433149</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,17 +1194,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,34 +1218,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112118128</v>
+        <v>112236100</v>
       </c>
       <c r="B7" t="n">
-        <v>95059</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,46 +1247,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338530</v>
+        <v>338598</v>
       </c>
       <c r="R7" t="n">
-        <v>6433165</v>
+        <v>6433091</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1371,12 +1309,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår efter spillkråka som födosökt vid stambasen på en högstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,34 +1328,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112118167</v>
+        <v>112118159</v>
       </c>
       <c r="B8" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,34 +1357,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1455,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338714</v>
+        <v>338583</v>
       </c>
       <c r="R8" t="n">
-        <v>6433095</v>
+        <v>6433160</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1495,7 +1430,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid basen av äldre gran. Gamla f k.</t>
+          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,15 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112118130</v>
+        <v>112118162</v>
       </c>
       <c r="B9" t="n">
-        <v>93269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,27 +1469,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1567,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338530</v>
+        <v>338583</v>
       </c>
       <c r="R9" t="n">
-        <v>6433165</v>
+        <v>6433160</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1607,7 +1542,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,15 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112118162</v>
+        <v>98803458</v>
       </c>
       <c r="B10" t="n">
-        <v>5145</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,46 +1581,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Slereboåns dalgångs NR, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338583</v>
+        <v>338502</v>
       </c>
       <c r="R10" t="n">
-        <v>6433159</v>
+        <v>6433126</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,17 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,27 +1660,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112221530</v>
+        <v>112010157</v>
       </c>
       <c r="B11" t="n">
-        <v>90842</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1702,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1799,14 +1714,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338720</v>
+        <v>338723</v>
       </c>
       <c r="R11" t="n">
-        <v>6433100</v>
+        <v>6433094</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,17 +1748,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca antal. Även övermogna fruktkroppar. Sannolikt samma där arten obsats tidigare i september.</t>
+          <t>Växte i mossig blåbärsgranskog med inslag av tall. 2 m till en medelgrov gran, 10 m till en medelgrov tall. 25 m åt nordost växte en stor Ramaria.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,54 +1774,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112221660</v>
+        <v>112221530</v>
       </c>
       <c r="B12" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1918,14 +1828,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om. , Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338727</v>
+        <v>338720</v>
       </c>
       <c r="R12" t="n">
-        <v>6433110</v>
+        <v>6433100</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,6 +1868,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca antal. Även övermogna fruktkroppar. Sannolikt samma där arten obsats tidigare i september.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,47 +1900,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112234897</v>
+        <v>112234239</v>
       </c>
       <c r="B13" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2033,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338737</v>
+        <v>338730</v>
       </c>
       <c r="R13" t="n">
-        <v>6433098</v>
+        <v>6433090</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,7 +1986,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte 2 m från en medelgrov gran och 6 m från en medelgrov tall. Stora delar av rörlagret var angripet och uppätet.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,42 +2014,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112234040</v>
+        <v>112613408</v>
       </c>
       <c r="B14" t="n">
-        <v>85238</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>249278</v>
+        <v>150</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2152,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338742</v>
+        <v>338726</v>
       </c>
       <c r="R14" t="n">
-        <v>6433095</v>
+        <v>6433094</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2182,17 +2090,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+          <t>Växte någon halvmeter från de grangråtickor som jag fann på platsen 2023-09-20. De gamla var det bara rester av, men dessa var lite yngre och kunde samlas in som kollekt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,42 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112283922</v>
+        <v>121359024</v>
       </c>
       <c r="B15" t="n">
-        <v>89139</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256756</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2271,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338719</v>
+        <v>338720</v>
       </c>
       <c r="R15" t="n">
-        <v>6433105</v>
+        <v>6433091</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2301,17 +2204,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Samma fruktkropp som jag såg 2023-09-09. Denna gången var den äldre och jag mätte den till 21 cm hög och 29 cm bred. 1,5 m från gran och 6-7 m från tall. Det stod ny ytterligare en blek taggsvamp, en yngre fruktkropp ca 25 meter längre söderut denna gång.</t>
+          <t>Växte på samma plats som förra året, invid en stigliknande formation med en liten kulle direkt söder om "stigen".</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,49 +2235,44 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin, Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112234006</v>
+        <v>121359908</v>
       </c>
       <c r="B16" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2390,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338742</v>
+        <v>338746</v>
       </c>
       <c r="R16" t="n">
-        <v>6433095</v>
+        <v>6433099</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2420,17 +2318,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En rejäl "tuva" med 75-100 fruktkroppar i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,71 +2349,62 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112233934</v>
+        <v>127816003</v>
       </c>
       <c r="B17" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>150</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338742</v>
+        <v>338721</v>
       </c>
       <c r="R17" t="n">
-        <v>6433095</v>
+        <v>6433102</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2539,17 +2428,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växte i en medelgrov granskog med inslag av framför allt tall. Växte 4 m från medelgrov tall, 2 m från klen gran och 4 m till medelgrov gran. Klart kalkpåverkad barrskog med flera andra kalkgynnade arter. Förekomst av blåsippa.</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,73 +2459,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112234871</v>
+        <v>112222297</v>
       </c>
       <c r="B18" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338747</v>
+        <v>338836</v>
       </c>
       <c r="R18" t="n">
-        <v>6433099</v>
+        <v>6433152</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2658,17 +2539,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte alldeles nära barrspindelskivling och blåsippa. Såg ut att vara den som bildar Mykorrhiza med gran, och gran stod närmast, men det stod även en medelgrov tall 8-10 m bort.</t>
+          <t>Ca 2 kvdm. I yngre grandominerad skog. Nära äldre parti.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,74 +2565,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112319644</v>
+        <v>112234006</v>
       </c>
       <c r="B19" t="n">
-        <v>95067</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>788</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>339683</v>
+        <v>338742</v>
       </c>
       <c r="R19" t="n">
-        <v>6433113</v>
+        <v>6433095</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2778,17 +2653,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 0,5 kvm.</t>
+          <t>En rejäl "tuva" med 75-100 fruktkroppar i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2804,66 +2679,68 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112319711</v>
+        <v>112411691</v>
       </c>
       <c r="B20" t="n">
-        <v>95067</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>788</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>339195</v>
+        <v>338738</v>
       </c>
       <c r="R20" t="n">
-        <v>6433104</v>
+        <v>6433093</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2890,17 +2767,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Några större tuvor.</t>
+          <t>Ett stort antal fruktkroppar satt gyttrat fördelade på några fläckar, ca 6 m väster om de djupa hjulspår som bäcken rinner i. 3 m till medelgrov tall och relativt grov gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,70 +2793,72 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112319668</v>
+        <v>119802411</v>
       </c>
       <c r="B21" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>788</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Söder om Mickelsdam, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>339565</v>
+        <v>338931</v>
       </c>
       <c r="R21" t="n">
-        <v>6433114</v>
+        <v>6433177</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3006,17 +2885,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vid basen av död gran mm</t>
+          <t>Sammanväxta fruktkroppar växande invind/på roten av gran i mossig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3025,55 +2904,56 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Otto Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112411671</v>
+        <v>121363230</v>
       </c>
       <c r="B22" t="n">
-        <v>79356</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>788</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3082,14 +2962,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>339623</v>
+        <v>338746</v>
       </c>
       <c r="R22" t="n">
-        <v>6433082</v>
+        <v>6433099</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3116,17 +2996,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
+          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,56 +3027,43 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112411540</v>
+        <v>121363305</v>
       </c>
       <c r="B23" t="n">
-        <v>83378</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3518</v>
+        <v>788</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3205,13 +3072,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>339392</v>
+        <v>338715</v>
       </c>
       <c r="R23" t="n">
-        <v>6433088</v>
+        <v>6433097</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3235,17 +3102,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växte i knappt medelgrov granskog med inslag av tall.</t>
+          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3266,58 +3133,52 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Thomas Grönlund, Linus Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112411466</v>
+        <v>112234138</v>
       </c>
       <c r="B24" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>2058</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3325,10 +3186,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>339209</v>
+        <v>338730</v>
       </c>
       <c r="R24" t="n">
-        <v>6433092</v>
+        <v>6433090</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3355,17 +3216,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växte på marken intill en hassel med havstulpanlav. Här börjar det bli lite blockigt och tallen ingår här lite mer i trädbeståndet än lite längre ner i sluttningen, där medelgrov gran dominerar stort.</t>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte 2 m från en medelgrov gran och 7 m från en medelgrov tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3393,47 +3254,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112411691</v>
+        <v>112234638</v>
       </c>
       <c r="B25" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>788</v>
+        <v>2058</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3444,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338738</v>
+        <v>338735</v>
       </c>
       <c r="R25" t="n">
-        <v>6433093</v>
+        <v>6433080</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3474,17 +3330,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ett stort antal fruktkroppar satt gyttrat fördelade på några fläckar, ca 6 m väster om de djupa hjulspår som bäcken rinner i. 3 m till medelgrov tall och relativt grov gran.</t>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte 7-8 m från de andra koppartaggsvamparna.  1 m från en klen gran och 3 m från en medelgrov gran. Växte bland husmossa och hultbräken.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,15 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112411553</v>
+        <v>112016572</v>
       </c>
       <c r="B26" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,33 +3379,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3564,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339646</v>
+        <v>339733</v>
       </c>
       <c r="R26" t="n">
-        <v>6433088</v>
+        <v>6433042</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3594,12 +3437,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Många kuddar av blåmossa, men de jag såg var ganska små.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3611,6 +3459,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Sydvänd brant med dominans av tall och ek</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3627,15 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112411563</v>
+        <v>112612271</v>
       </c>
       <c r="B27" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3643,31 +3496,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3679,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339703</v>
+        <v>339627</v>
       </c>
       <c r="R27" t="n">
-        <v>6433086</v>
+        <v>6433093</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3709,17 +3562,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växte i flera fläckar inom en radie på 10 m. ganska mycket.</t>
+          <t>En lite större kudde som var 30 cm hög, 80 cm lång och 60 cm bred. Växte i skog med gran, tall och ek, lite norr om en sydvänd brant. Ganska lång trädkontinuitet med andra ord.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3747,15 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112411670</v>
+        <v>129027094</v>
       </c>
       <c r="B28" t="n">
-        <v>95488</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,41 +3611,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339608</v>
+        <v>338689</v>
       </c>
       <c r="R28" t="n">
-        <v>6433081</v>
+        <v>6433092</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3821,17 +3665,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växte på en ek, strax ovanför den sydvända branten.</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,34 +3689,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112411635</v>
+        <v>95154947</v>
       </c>
       <c r="B29" t="n">
-        <v>79356</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3875,40 +3718,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>2387</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>kärret mellan Slereboåns och Skårs, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339209</v>
+        <v>339069</v>
       </c>
       <c r="R29" t="n">
-        <v>6433092</v>
+        <v>6433151</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3932,17 +3784,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3958,27 +3805,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Pielach, Peter Carlsson, Bo Nilsson, Elke Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112431338</v>
+        <v>112016831</v>
       </c>
       <c r="B30" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,43 +3828,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>338710</v>
+        <v>339518</v>
       </c>
       <c r="R30" t="n">
-        <v>6433103</v>
+        <v>6433053</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4049,17 +3894,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I senvuxen, klen gran.</t>
+          <t>Växte i skog med klen-medelgrov gran och björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,27 +3920,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112612655</v>
+        <v>112319644</v>
       </c>
       <c r="B31" t="n">
-        <v>79468</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,37 +3943,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2569</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>339754</v>
+        <v>339683</v>
       </c>
       <c r="R31" t="n">
-        <v>6433067</v>
+        <v>6433112</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4160,17 +4009,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växte på en av tre klena ekar som växte ihop.</t>
+          <t>Ca 0,5 kvm.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,27 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112612271</v>
+        <v>112319711</v>
       </c>
       <c r="B32" t="n">
-        <v>93798</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,46 +4058,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>339627</v>
+        <v>339195</v>
       </c>
       <c r="R32" t="n">
-        <v>6433093</v>
+        <v>6433103</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4280,17 +4116,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>En lite större kudde som var 30 cm hög, 80 cm lång och 60 cm bred. Växte i skog med gran, tall och ek, lite norr om en sydvänd brant. Ganska lång trädkontinuitet med andra ord.</t>
+          <t>Några större tuvor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4306,62 +4142,58 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112613408</v>
+        <v>112411466</v>
       </c>
       <c r="B33" t="n">
-        <v>91021</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>150</v>
+        <v>2569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4369,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>338726</v>
+        <v>339209</v>
       </c>
       <c r="R33" t="n">
-        <v>6433094</v>
+        <v>6433092</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4399,17 +4231,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växte någon halvmeter från de grangråtickor som jag fann på platsen 2023-09-20. De gamla var det bara rester av, men dessa var lite yngre och kunde samlas in som kollekt.</t>
+          <t>Växte på marken intill en hassel med havstulpanlav. Här börjar det bli lite blockigt och tallen ingår här lite mer i trädbeståndet än lite längre ner i sluttningen, där medelgrov gran dominerar stort.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4437,15 +4269,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120110526</v>
+        <v>112411553</v>
       </c>
       <c r="B34" t="n">
-        <v>96198</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4472,7 +4299,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4485,14 +4312,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>339514</v>
+        <v>339646</v>
       </c>
       <c r="R34" t="n">
-        <v>6433090</v>
+        <v>6433088</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4519,17 +4346,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4557,15 +4379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120110576</v>
+        <v>112411563</v>
       </c>
       <c r="B35" t="n">
-        <v>96198</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4592,12 +4409,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4605,14 +4422,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>339497</v>
+        <v>339703</v>
       </c>
       <c r="R35" t="n">
-        <v>6433101</v>
+        <v>6433086</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4639,12 +4456,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Växte i flera fläckar inom en radie på 10 m. ganska mycket.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4672,47 +4494,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120110497</v>
+        <v>120110526</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4760,7 +4581,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Invid en högstubbe med spillkråkehack vid basen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,6 +4590,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4787,61 +4609,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121359908</v>
+        <v>120110576</v>
       </c>
       <c r="B37" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>150</v>
+        <v>2569</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>338746</v>
+        <v>339497</v>
       </c>
       <c r="R37" t="n">
-        <v>6433099</v>
+        <v>6433101</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4868,17 +4686,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växte på en ny plats jämfört med de platser jag fann grangråticka på förra året. Fruktkroppen stod 1 m väster om platsen där bäcken rinner i hjulspåret. Platsen ligger mer än 10 m från de andra grangråtickeplatserna. 3 m till en medelgrov gran. Växte bara ett par meter från en hel del gul taggsvamp.</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4899,63 +4712,55 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121363230</v>
+        <v>128623098</v>
       </c>
       <c r="B38" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>788</v>
+        <v>2569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>338746</v>
+        <v>338872</v>
       </c>
       <c r="R38" t="n">
-        <v>6433099</v>
+        <v>6433142</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4979,17 +4784,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>5 gyttrigare av grumtkroppar som satt taktegellagda. Ganska många fruktkroppar, totalt sett. Växte 2 m väster om hjulspåret i vilken bäcken rinner. 3-5 m från medelgrov gran.</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4998,72 +4808,63 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121363305</v>
+        <v>129025839</v>
       </c>
       <c r="B39" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>788</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>338715</v>
+        <v>338674</v>
       </c>
       <c r="R39" t="n">
-        <v>6433097</v>
+        <v>6433139</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5090,17 +4891,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>En stor gyttrig med taktegellagda fruktkroppar växte 1,5 m SO om en relativt grov gran, 5 m NV om de närmaste 7 grangråtickorna vid den stigliknande formationen.</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5109,29 +4915,33 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Thomas Grönlund, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127813879</v>
+        <v>129027040</v>
       </c>
       <c r="B40" t="n">
-        <v>95813</v>
+        <v>97733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5139,21 +4949,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5163,13 +4973,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>338706</v>
+        <v>338685</v>
       </c>
       <c r="R40" t="n">
-        <v>6433103</v>
+        <v>6433091</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5193,22 +5003,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5235,55 +5045,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127816003</v>
+        <v>129027300</v>
       </c>
       <c r="B41" t="n">
-        <v>92731</v>
+        <v>97733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>150</v>
+        <v>2569</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>338721</v>
+        <v>338683</v>
       </c>
       <c r="R41" t="n">
-        <v>6433102</v>
+        <v>6433074</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5307,22 +5110,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,7 +5139,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5350,10 +5157,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127820719</v>
+        <v>129116793</v>
       </c>
       <c r="B42" t="n">
-        <v>57679</v>
+        <v>97733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5361,51 +5168,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102977</v>
+        <v>2569</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>338683</v>
+        <v>338996</v>
       </c>
       <c r="R42" t="n">
-        <v>6433100</v>
+        <v>6433143</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5429,12 +5222,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5461,10 +5264,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128623143</v>
+        <v>129116850</v>
       </c>
       <c r="B43" t="n">
-        <v>97530</v>
+        <v>97733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,41 +5275,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>338866</v>
+        <v>338979</v>
       </c>
       <c r="R43" t="n">
-        <v>6433122</v>
+        <v>6433162</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5530,22 +5329,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5572,10 +5371,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128623459</v>
+        <v>112411639</v>
       </c>
       <c r="B44" t="n">
-        <v>97530</v>
+        <v>97394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,41 +5382,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>2590</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>338878</v>
+        <v>339819</v>
       </c>
       <c r="R44" t="n">
-        <v>6433141</v>
+        <v>6433100</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5641,22 +5440,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>18:23</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>18:23</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växte på en klen låga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5665,28 +5459,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128623098</v>
+        <v>112613636</v>
       </c>
       <c r="B45" t="n">
-        <v>97280</v>
+        <v>97394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5694,37 +5489,53 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>338872</v>
+        <v>339233</v>
       </c>
       <c r="R45" t="n">
-        <v>6433142</v>
+        <v>6433088</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5748,22 +5559,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>18:09</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>18:09</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Växte på en klen granlåga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5772,75 +5578,83 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129026915</v>
+        <v>112613663</v>
       </c>
       <c r="B46" t="n">
-        <v>57887</v>
+        <v>97394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>338675</v>
+        <v>339711</v>
       </c>
       <c r="R46" t="n">
-        <v>6433103</v>
+        <v>6433055</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5864,22 +5678,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växte på en medelgrov låga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5888,28 +5697,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129025873</v>
+        <v>112016353</v>
       </c>
       <c r="B47" t="n">
-        <v>97598</v>
+        <v>97785</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5917,38 +5727,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>338669</v>
+        <v>339733</v>
       </c>
       <c r="R47" t="n">
-        <v>6433141</v>
+        <v>6433042</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5975,22 +5785,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På ek i en sydvänd brant. Fin tall- och ekmiljö med äldre träd samt torrträd, högstubbar och lågor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5999,28 +5804,39 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Äldre tallar och ekar och gott om död ved i sydvänd brant</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129025839</v>
+        <v>112016639</v>
       </c>
       <c r="B48" t="n">
-        <v>97348</v>
+        <v>97785</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6028,34 +5844,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>338674</v>
+        <v>339697</v>
       </c>
       <c r="R48" t="n">
-        <v>6433139</v>
+        <v>6433038</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6082,22 +5902,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växte på ekar högt upp i den sydvända branten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6106,33 +5921,39 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Sydvänd brant med dominans av ek och tall</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129025860</v>
+        <v>112319617</v>
       </c>
       <c r="B49" t="n">
-        <v>95963</v>
+        <v>97785</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6140,37 +5961,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>338675</v>
+        <v>339475</v>
       </c>
       <c r="R49" t="n">
-        <v>6433142</v>
+        <v>6433150</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,22 +6019,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På en senvuxen ek i barrskogen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,33 +6038,44 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129116850</v>
+        <v>112411670</v>
       </c>
       <c r="B50" t="n">
-        <v>97348</v>
+        <v>97785</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6252,37 +6083,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>338979</v>
+        <v>339608</v>
       </c>
       <c r="R50" t="n">
-        <v>6433162</v>
+        <v>6433081</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6306,22 +6141,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Växte på en ek, strax ovanför den sydvända branten.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6330,21 +6160,4286 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>95154960</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97844</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2617</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Flikbålmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Riccardia multifida</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>kärret mellan Slereboåns och Skårs, Vg</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>339069</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6433151</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anna Pielach, Peter Carlsson, Bo Nilsson, Elke Nilsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127813879</v>
+      </c>
+      <c r="B52" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>338706</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Grimhild Angertuva</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Grimhild Angertuva</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129025860</v>
+      </c>
+      <c r="B53" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>338675</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6433142</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>112222310</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>338745</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6433065</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 mycel.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>112411404</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>338746</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6433079</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Växte i medelgrov granskog med inslag av medelgrov tall, bland kransmossa, husmossa och harsyra. 2 m från gran och 9 m från tall. Denna del av skogen är kalkpåverkad och flera kalkgynnade arter har noterats i sluttningen ner till den lilla bäcken.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112411540</v>
+      </c>
+      <c r="B56" t="n">
+        <v>85274</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>339392</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6433088</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växte i knappt medelgrov granskog med inslag av tall.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1439777</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Risveden, Skår 1:39, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>339397</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6433141</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2010-08-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2010-08-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>fultig granskog</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>Leif Danielson</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Leif Danielson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Leif Danielson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>94983318</v>
+      </c>
+      <c r="B58" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hydnellum, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>339361</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6433082</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>gles granskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>112234301</v>
+      </c>
+      <c r="B59" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>338730</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6433090</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Växte intill grangråtickorna i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte 2 m från en medelgrov gran och 6 m från en medelgrov tall.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>112411681</v>
+      </c>
+      <c r="B60" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>338731</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6433087</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Växte vid sillkremlan.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121363281</v>
+      </c>
+      <c r="B61" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>338735</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6433089</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Växte ett par meter öster om platsen med 1 fruktkropp av grangråticka där jag förra året fann koppartaggsvamp och grangråticka.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund, Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>112234066</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>338789</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6433091</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Växte nedanför en hög sydvänd brant med lodytor. Strax söderom rinner en liten bäck genom ett alkärr. Växte 1 m från en medelgrov gran.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>112118167</v>
+      </c>
+      <c r="B63" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>338713</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6433095</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Vid basen av äldre gran. Gamla f k.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>112118170</v>
+      </c>
+      <c r="B64" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>338724</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6433096</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ett mycel. Även färsk f k.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>112221660</v>
+      </c>
+      <c r="B65" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, söder om. , Vg</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>338727</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6433110</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>112234871</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>338747</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6433099</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen. Växte alldeles nära barrspindelskivling och blåsippa. Såg ut att vara den som bildar Mykorrhiza med gran, och gran stod närmast, men det stod även en medelgrov tall 8-10 m bort.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>112411385</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>338746</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6433079</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Den som går med gran. Växte i medelgrov granskog med inslag av medelgrov tall, 2 m från gran och 8 m till medelgrov tall. Denna sluttning är kalkpåverkad och flera kalkgynnade arter stod i sluttningen.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>112016525</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Röserna, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>339733</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6433042</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spår efter spillkråka vid stambasen hos tall i sydvänd brant.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Tall och ek i sydvänd brant</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>112319668</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>339565</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6433114</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Vid basen av död gran mm</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120110497</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>339514</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6433090</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127820719</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>338683</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6433100</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>112319655</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>339683</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6433112</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>112411685</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>338745</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6433077</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>112431347</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>338735</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6433080</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 2 ex.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127817601</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>338727</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6433070</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129026915</v>
+      </c>
+      <c r="B76" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>338675</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S76" t="n">
+        <v>7</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>112431338</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>338710</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I senvuxen, klen gran.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128623143</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>338866</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6433122</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128623459</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>338878</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6433141</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129025873</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>338669</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6433141</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>112234897</v>
+      </c>
+      <c r="B81" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>338737</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6433098</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128621998</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>338883</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6433164</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128622113</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>338884</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6433165</v>
+      </c>
+      <c r="S83" t="n">
+        <v>8</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128622404</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>338884</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6433164</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>112411635</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>339209</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6433092</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>112411671</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Röserna, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>339623</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6433082</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>112612655</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Röserna, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>339754</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6433067</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Växte på en av tre klena ekar som växte ihop.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>112234040</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>338742</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6433095</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112010157</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234239</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112613408</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127816003</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112222297</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234006</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411691</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1928,6 +1983,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119802411</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121363230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2140,6 +2205,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121363305</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234138</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2368,6 +2443,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234638</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2485,6 +2565,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112016572</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2600,6 +2685,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112612271</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2707,6 +2797,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129027094</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2817,6 +2912,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95154947</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2934,6 +3034,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964643</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3049,6 +3154,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112016831</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3159,6 +3269,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118128</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3274,6 +3389,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112235807</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3389,6 +3509,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319644</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3496,6 +3621,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319711</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3611,6 +3741,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411466</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3721,6 +3856,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411553</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3836,6 +3976,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411563</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3951,6 +4096,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120110526</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4061,6 +4211,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120110576</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4168,6 +4323,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128623098</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4280,6 +4440,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129025839</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4387,6 +4552,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129027040</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4499,6 +4669,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129027300</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4606,6 +4781,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116793</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4713,6 +4893,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116850</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4820,6 +5005,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411639</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4939,6 +5129,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112613636</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5058,6 +5253,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112613663</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5175,6 +5375,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112016353</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5292,6 +5497,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112016639</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5414,6 +5624,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319617</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5521,6 +5736,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411670</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5631,6 +5851,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95154960</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5738,6 +5963,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118130</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5845,6 +6075,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813879</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5957,6 +6192,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129025860</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6071,6 +6311,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112222310</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6185,6 +6430,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411404</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6299,6 +6549,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411540</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6421,6 +6676,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1439777</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6535,6 +6795,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94983318</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6649,6 +6914,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234301</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6755,6 +7025,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411681</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6869,6 +7144,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121363281</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6983,6 +7263,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234066</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7097,6 +7382,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118167</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7211,6 +7501,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118170</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7320,6 +7615,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221660</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7434,6 +7734,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234871</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7548,6 +7853,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411385</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7660,6 +7970,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106197313</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7780,6 +8095,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112016525</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7890,6 +8210,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112236100</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8000,6 +8325,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319668</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8110,6 +8440,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120110497</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8222,6 +8557,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118159</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8333,6 +8673,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820719</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8452,6 +8797,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319655</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8553,6 +8903,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411685</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8677,6 +9032,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112431347</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8784,6 +9144,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127817601</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8900,6 +9265,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129026915</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9012,6 +9382,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112118162</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9124,6 +9499,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112431338</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9226,6 +9606,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98803458</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9337,6 +9722,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128623143</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9448,6 +9838,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128623459</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9559,6 +9954,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129025873</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9670,6 +10070,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234897</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9781,6 +10186,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621998</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9897,6 +10307,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622113</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10008,6 +10423,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622404</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10114,6 +10534,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411635</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10220,6 +10645,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112411671</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10326,6 +10756,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112612655</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10440,8 +10875,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234040</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>